--- a/inst/validation/templates/uat_cases.xlsx
+++ b/inst/validation/templates/uat_cases.xlsx
@@ -67,7 +67,7 @@
     <t>FR-PL009;FR-PL010;FR-PL240</t>
   </si>
   <si>
-    <t>1) Use the RTF of UAT-001. 2) Compare each statistic with a summary computed independently from the same ADSL (for example with base R aggregate()).</t>
+    <t>1) Use the RTF of UAT-001. 2) Compare each statistic with a summary computed independently from the same ADSL (pharmaverseadam::adsl, SAFFL == 'Y') (for example with base R aggregate()).</t>
   </si>
   <si>
     <t>Every n, mean, SD, median, quartile, minimum, maximum and percentage equals the independent summary, with the decimals the program declares.</t>
@@ -112,7 +112,7 @@
     <t>FR-PL002;FR-PL144;FR-PL147</t>
   </si>
   <si>
-    <t>1) Use the RTF of UAT-004. 2) Count the preferred terms at 5% or more in any arm independently from ADAE and ADSL.</t>
+    <t>1) Use the RTF of UAT-004. 2) Count the preferred terms at 5% or more in any arm independently from the same ADAE and ADSL (treatment-emergent, safety population; percentages of the arm's N).</t>
   </si>
   <si>
     <t>The table holds exactly the PTs counted independently, each under its SOC; no SOC is left without a PT.</t>
@@ -130,7 +130,7 @@
     <t>1) Take the plan of UAT-004 and change plan_filter(p &gt;= 0.05) to plan_filter(p &gt;= 2) (no term passes). 2) Add plan_empty() to the plan. 3) Write the RTF and open it.</t>
   </si>
   <si>
-    <t>The table has one row reading 'No subjects met the criteria.' (or the text given) and its column header.</t>
+    <t>Below the 'Subjects with at least one TEAE' row (kept, with its counts) one row reads 'No subjects met the criteria.' (or the text given); there is no SOC or PT row, and the column header is printed.</t>
   </si>
   <si>
     <t>UAT-007</t>
@@ -142,10 +142,10 @@
     <t>FR-PL027;FR-PL480;FR-PL481;FR-PL483</t>
   </si>
   <si>
-    <t>1) Take cards::ADAE (first 60 records). 2) table_plan(adae) |&gt; plan_listing(listing_col('USUBJID', width = 12), listing_col('AEDECOD', width = 20), listing_col('AETERM', width = 10)) |&gt; plan_paginate_rows(max_rows = 20) |&gt; plan_titles('Listing 16.2.7', 'Adverse events') . 3) rtf_document() |&gt; rtf_tables(plan) |&gt; generate_rtfreport(file). 4) Open the RTF.</t>
-  </si>
-  <si>
-    <t>AETERM text longer than its column wraps onto further lines within the column; every page has at most 20 records and repeats the column header; titles on every page. Visual check.</t>
+    <t>1) Take cards::ADAE (first 60 records). 2) table_plan(adae) |&gt; plan_listing(listing_col('USUBJID', width = 12), listing_col('AEDECOD', width = 20), listing_col('AETERM', width = 10)) |&gt; plan_paginate_rows(max_rows = 20) |&gt; plan_titles('Listing 16.2.7', 'Adverse events'). 3) rtf_document() |&gt; rtf_tables(plan) |&gt; generate_rtfreport(file). 4) Open the RTF.</t>
+  </si>
+  <si>
+    <t>AETERM text longer than its column wraps onto further lines within the column; every page holds at most 20 lines (each line of wrapped text counts, and so does the blank line after each record), and no record is split across two pages; every page repeats the column header and the two title lines. Visual check.</t>
   </si>
   <si>
     <t>UAT-008</t>
@@ -169,7 +169,7 @@
     <t>UR-006</t>
   </si>
   <si>
-    <t>FR-IX111;FR-IX123</t>
+    <t>FR-IX123;FR-IX266</t>
   </si>
   <si>
     <t>1) Use the RTF of UAT-004 (several pages). 2) Open it in Word and look at the header and footer of the first, a middle and the last page.</t>
@@ -187,10 +187,10 @@
     <t>FR-PL028;FR-PL486</t>
   </si>
   <si>
-    <t>1) Use the RTF of UAT-004. 2) Look at the titles and footnotes on every page.</t>
-  </si>
-  <si>
-    <t>The three title lines are above the table and the footnotes below it on every page. Visual check.</t>
+    <t>1) Take the plan of UAT-007 and add plan_footnotes('Source: cards::ADAE (dummy data)'). 2) rtf_document() |&gt; rtf_tables(plan) |&gt; generate_rtfreport(file). 3) Open the RTF and look at every page.</t>
+  </si>
+  <si>
+    <t>The two title lines ('Listing 16.2.7', 'Adverse events') are above the listing and the footnote below it, on every page. Visual check.</t>
   </si>
   <si>
     <t>UAT-011</t>
@@ -217,10 +217,10 @@
     <t>FR-PL024;FR-PL449;FR-PL450;FR-PL453</t>
   </si>
   <si>
-    <t>1) Take the plan of UAT-001; add plan_paginate_group(col = 'group', heading = '{value}') before plan_stub(). 2) rtf_document() |&gt; rtf_tables(plan, auto_section = TRUE) |&gt; generate_rtfreport(file). 3) Open the RTF and its navigation pane.</t>
-  </si>
-  <si>
-    <t>One section per characteristic, each starting on a new page and named with its value. Visual check.</t>
+    <t>1) In the program of UAT-001 add plan_paginate_group(col = 'group', heading = '{value}') before plan_stub(). 2) rtf_document() |&gt; rtf_tables(tbl_plan, auto_section = TRUE) |&gt; generate_rtfreport(file). 3) Open the RTF and its navigation pane.</t>
+  </si>
+  <si>
+    <t>One section per characteristic (Age (years); Age group, n (%); Sex, n (%); Race, n (%)), each starting on a new page and named with its label. Visual check.</t>
   </si>
   <si>
     <t>UAT-013</t>
@@ -229,13 +229,13 @@
     <t>UR-013</t>
   </si>
   <si>
-    <t>FR-PL025;FR-PL461;FR-PL465</t>
-  </si>
-  <si>
-    <t>1) Take the plan of UAT-001 with eight more arms (or a lab table with one column per visit) so that it is wider than the page. 2) Add plan_paginate_cols(keep = 'Characteristic'). 3) Write the RTF and open it.</t>
-  </si>
-  <si>
-    <t>The columns are split into blocks that fit the page width; every block repeats the Characteristic column and its part of the header. Visual check.</t>
+    <t>FR-PL025;FR-PL461;FR-PL464;FR-PL465</t>
+  </si>
+  <si>
+    <t>1) Take the plan of UAT-001 and add plan_paginate_cols(every = 2, keep = 'Characteristic'), which cuts the columns as a table too wide for the page is cut. 2) Write the RTF and open it.</t>
+  </si>
+  <si>
+    <t>The columns are split into blocks of two (Placebo and Xanomeline Low Dose; Xanomeline High Dose and Total; the p-value column), one block a page; every block repeats the Characteristic column and its part of the column header. Visual check.</t>
   </si>
   <si>
     <t>UAT-014</t>
@@ -259,7 +259,7 @@
     <t>FR-PL005;FR-IX132</t>
   </si>
   <si>
-    <t>1) In the program of UAT-007 run it twice to two files. 2) Compare the two files' checksums with tools::md5sum().</t>
+    <t>1) Run the program of UAT-007 twice, to two files. 2) unname(tools::md5sum(c(file1, file2))) -- compare the two checksums.</t>
   </si>
   <si>
     <t>UAT-016</t>
